--- a/system_development/v0.2.0/BOM-v0.2.0 .xlsx
+++ b/system_development/v0.2.0/BOM-v0.2.0 .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06027168005bd3d0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Fieldable-NV-Center\system_development\v0.2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{755B4C13-B223-434B-B2AB-C73C191B927A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34D7EF5D-3ECB-46C0-B9D1-26FAD05DDD26}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B72C54F-B337-4E7C-B9BF-535EE0699C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="189">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -600,6 +600,9 @@
   </si>
   <si>
     <t>https://www.artisantg.com/93448-1/Teledyne-ADE-T-2S63T-6?srsltid=AU7gw4XNEMGgzwftKMnx5biFnNaDLx9G4aET42T8VpQcZWK-BH7_IYnq</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/358125015615?_skw=high+power+microwave++amplifier&amp;itmmeta=01M4RF5DBBS0HB0VZX34TEKM0D&amp;hash=item5361ea123f:g:fqMAAeSwqg1pqPXO&amp;itmprp=enc%3AAQALAAABACHNgUiiE%2FjQhlDTaMiAde9gnJ1rXlNv--UBtlcfqI4tE9JJmrwBjNnDriTothTowuafHey3eyuQlCkcAApZmT0K9P6PnLzXHaCWY391W2MOR0XaipgxuZ5LSu1W%2FiDQU4NHojUvlUEST9CYQOFRWufGeHPfSactJFJxVHxH2ucuEuTwptjkwreUYVXrHzeulp4mIj%2BTrEheXNywZeOnulWnG1yljSxCsK%2BU55AfKvcNpZJ5w6rpMeBd%2B5%2BIDci6ZsyQpaNHkalobk%2BcN7UzVCf35lfRbAdZuylTTiszIHtL%2Bms%2Fw5uLO1oM3axhr2cWKJ%2FO3zbJAIhlDYDNpJrzu78%3D%7Ctkp%3ABk9SR_jVlY-maA</t>
   </si>
 </sst>
 </file>
@@ -700,7 +703,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -774,6 +777,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1111,26 +1119,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:N47"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N48"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="62.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="62.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="87.5546875" customWidth="1"/>
-    <col min="10" max="10" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="83.44140625" customWidth="1"/>
-    <col min="12" max="12" width="62.44140625" customWidth="1"/>
-    <col min="13" max="13" width="55.88671875" customWidth="1"/>
+    <col min="9" max="9" width="87.5703125" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.42578125" customWidth="1"/>
+    <col min="12" max="12" width="62.42578125" customWidth="1"/>
+    <col min="13" max="13" width="55.85546875" customWidth="1"/>
     <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -1174,7 +1182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>17</v>
       </c>
@@ -1197,12 +1205,12 @@
         <v>188.12</v>
       </c>
       <c r="H2" s="5"/>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="28" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>66</v>
       </c>
@@ -1225,12 +1233,12 @@
         <v>1043.25</v>
       </c>
       <c r="H3" s="5"/>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="28" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1260,7 +1268,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1283,14 +1291,14 @@
         <v>137.27000000000001</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="28" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1313,11 +1321,11 @@
         <v>88.34</v>
       </c>
       <c r="H6" s="5"/>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>69</v>
       </c>
@@ -1340,12 +1348,12 @@
         <v>202.1</v>
       </c>
       <c r="H7" s="5"/>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="28" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>70</v>
       </c>
@@ -1369,12 +1377,12 @@
         <v>134.34</v>
       </c>
       <c r="H8" s="5"/>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="28" t="s">
         <v>39</v>
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>71</v>
       </c>
@@ -1398,12 +1406,12 @@
         <v>57.2</v>
       </c>
       <c r="H9" s="5"/>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>43</v>
       </c>
@@ -1427,12 +1435,12 @@
         <v>1897.73</v>
       </c>
       <c r="H10" s="5"/>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="28" t="s">
         <v>46</v>
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>43</v>
       </c>
@@ -1456,12 +1464,12 @@
         <v>4091.98</v>
       </c>
       <c r="H11" s="5"/>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="28" t="s">
         <v>49</v>
       </c>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>72</v>
       </c>
@@ -1485,12 +1493,12 @@
         <v>234.2</v>
       </c>
       <c r="H12" s="5"/>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="28" t="s">
         <v>52</v>
       </c>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>53</v>
       </c>
@@ -1514,12 +1522,12 @@
         <v>120</v>
       </c>
       <c r="H13" s="5"/>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="28" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>73</v>
       </c>
@@ -1543,12 +1551,12 @@
         <v>17.62</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="28" t="s">
         <v>59</v>
       </c>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>74</v>
       </c>
@@ -1572,11 +1580,11 @@
         <v>1350</v>
       </c>
       <c r="H15" s="5"/>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>75</v>
       </c>
@@ -1600,12 +1608,12 @@
         <v>381.34</v>
       </c>
       <c r="H16" s="5"/>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="27" t="s">
         <v>65</v>
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>76</v>
       </c>
@@ -1629,12 +1637,12 @@
         <v>214.81</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="27" t="s">
         <v>79</v>
       </c>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>81</v>
       </c>
@@ -1658,13 +1666,13 @@
         <v>119.18</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="27" t="s">
         <v>83</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>84</v>
       </c>
@@ -1688,13 +1696,13 @@
         <v>80.16</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="27" t="s">
         <v>87</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>88</v>
       </c>
@@ -1718,13 +1726,13 @@
         <v>61.29</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="27" t="s">
         <v>91</v>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>92</v>
       </c>
@@ -1748,13 +1756,13 @@
         <v>4406.82</v>
       </c>
       <c r="H21" s="11"/>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="27" t="s">
         <v>95</v>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
         <v>96</v>
       </c>
@@ -1778,13 +1786,13 @@
         <v>3764.68</v>
       </c>
       <c r="H22" s="11"/>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="27" t="s">
         <v>99</v>
       </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
         <v>101</v>
       </c>
@@ -1808,13 +1816,13 @@
         <v>2480.25</v>
       </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="27" t="s">
         <v>103</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
         <v>106</v>
       </c>
@@ -1838,13 +1846,13 @@
         <v>662.5</v>
       </c>
       <c r="H24" s="11"/>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="27" t="s">
         <v>107</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>108</v>
       </c>
@@ -1868,11 +1876,11 @@
         <v>84.12</v>
       </c>
       <c r="H25" s="4"/>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="27" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>108</v>
       </c>
@@ -1896,11 +1904,11 @@
         <v>84.12</v>
       </c>
       <c r="H26" s="4"/>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="27" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>112</v>
       </c>
@@ -1924,11 +1932,11 @@
         <v>607.58000000000004</v>
       </c>
       <c r="H27" s="4"/>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="27" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>120</v>
       </c>
@@ -1952,11 +1960,11 @@
         <v>382.59</v>
       </c>
       <c r="H28" s="4"/>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="27" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>127</v>
       </c>
@@ -1980,11 +1988,11 @@
         <v>169.26</v>
       </c>
       <c r="H29" s="4"/>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="27" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>126</v>
       </c>
@@ -2008,11 +2016,11 @@
         <v>169.26</v>
       </c>
       <c r="H30" s="4"/>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="27" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>131</v>
       </c>
@@ -2036,11 +2044,11 @@
         <v>21.21</v>
       </c>
       <c r="H31" s="4"/>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="27" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>139</v>
       </c>
@@ -2064,11 +2072,11 @@
         <v>109.65</v>
       </c>
       <c r="H32" s="4"/>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="27" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>138</v>
       </c>
@@ -2092,11 +2100,11 @@
         <v>960.79</v>
       </c>
       <c r="H33" s="4"/>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="27" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>143</v>
       </c>
@@ -2120,11 +2128,11 @@
         <v>1925.49</v>
       </c>
       <c r="H34" s="4"/>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="27" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>147</v>
       </c>
@@ -2148,11 +2156,11 @@
         <v>5260</v>
       </c>
       <c r="H35" s="4"/>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="27" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>152</v>
       </c>
@@ -2176,11 +2184,11 @@
         <v>600.27</v>
       </c>
       <c r="H36" s="4"/>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="27" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>155</v>
       </c>
@@ -2204,11 +2212,11 @@
         <v>20.84</v>
       </c>
       <c r="H37" s="4"/>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="27" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>159</v>
       </c>
@@ -2231,11 +2239,11 @@
         <v>1270</v>
       </c>
       <c r="H38" s="4"/>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="27" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>170</v>
       </c>
@@ -2258,11 +2266,11 @@
         <v>199.99</v>
       </c>
       <c r="H39" s="4"/>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="27" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>166</v>
       </c>
@@ -2285,11 +2293,11 @@
         <v>134.65</v>
       </c>
       <c r="H40" s="4"/>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="27" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>174</v>
       </c>
@@ -2306,9 +2314,9 @@
       <c r="F41" s="15"/>
       <c r="G41" s="9"/>
       <c r="H41" s="4"/>
-      <c r="I41" s="3"/>
-    </row>
-    <row r="42" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="27"/>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>173</v>
       </c>
@@ -2325,9 +2333,9 @@
       <c r="F42" s="15"/>
       <c r="G42" s="9"/>
       <c r="H42" s="4"/>
-      <c r="I42" s="3"/>
-    </row>
-    <row r="43" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I42" s="27"/>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>175</v>
       </c>
@@ -2350,11 +2358,11 @@
         <v>178</v>
       </c>
       <c r="H43" s="4"/>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="27" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>179</v>
       </c>
@@ -2377,11 +2385,11 @@
         <v>1725.15</v>
       </c>
       <c r="H44" s="4"/>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="27" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>179</v>
       </c>
@@ -2397,41 +2405,51 @@
       <c r="E45" s="14">
         <v>1</v>
       </c>
-      <c r="F45" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>178</v>
+      <c r="F45" s="15">
+        <v>344.22</v>
+      </c>
+      <c r="G45" s="23">
+        <f>F45*E45</f>
+        <v>344.22</v>
       </c>
       <c r="H45" s="4"/>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="27" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J45" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="17"/>
       <c r="D46" s="26"/>
       <c r="E46" s="14"/>
       <c r="F46" s="15"/>
       <c r="G46" s="23"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="3"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I46" s="27"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F47" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="5">
         <f>SUM(G2:G45)</f>
-        <v>36500.17</v>
-      </c>
+        <v>36844.39</v>
+      </c>
+      <c r="I47" s="29"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I48" s="29"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{755CDB9E-DA93-4B70-9710-BE1D1CAFA340}"/>
+    <hyperlink ref="I45" r:id="rId2" xr:uid="{1B8C0853-3464-48CE-96BF-1FE1938285A5}"/>
+    <hyperlink ref="J45" r:id="rId3" display="https://www.ebay.com/itm/358125015615?_skw=high+power+microwave++amplifier&amp;itmmeta=01M4RF5DBBS0HB0VZX34TEKM0D&amp;hash=item5361ea123f:g:fqMAAeSwqg1pqPXO&amp;itmprp=enc%3AAQALAAABACHNgUiiE%2FjQhlDTaMiAde9gnJ1rXlNv--UBtlcfqI4tE9JJmrwBjNnDriTothTowuafHey3eyuQlCkcAApZmT0K9P6PnLzXHaCWY391W2MOR0XaipgxuZ5LSu1W%2FiDQU4NHojUvlUEST9CYQOFRWufGeHPfSactJFJxVHxH2ucuEuTwptjkwreUYVXrHzeulp4mIj%2BTrEheXNywZeOnulWnG1yljSxCsK%2BU55AfKvcNpZJ5w6rpMeBd%2B5%2BIDci6ZsyQpaNHkalobk%2BcN7UzVCf35lfRbAdZuylTTiszIHtL%2Bms%2Fw5uLO1oM3axhr2cWKJ%2FO3zbJAIhlDYDNpJrzu78%3D%7Ctkp%3ABk9SR_jVlY-maA" xr:uid="{894ADAD7-C5E5-464A-B79C-BFECFB51247F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/system_development/v0.2.0/BOM-v0.2.0 .xlsx
+++ b/system_development/v0.2.0/BOM-v0.2.0 .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Fieldable-NV-Center\system_development\v0.2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B72C54F-B337-4E7C-B9BF-535EE0699C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E319474E-4949-4766-BA60-60104250321C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="190">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -603,6 +603,9 @@
   </si>
   <si>
     <t>https://www.ebay.com/itm/358125015615?_skw=high+power+microwave++amplifier&amp;itmmeta=01M4RF5DBBS0HB0VZX34TEKM0D&amp;hash=item5361ea123f:g:fqMAAeSwqg1pqPXO&amp;itmprp=enc%3AAQALAAABACHNgUiiE%2FjQhlDTaMiAde9gnJ1rXlNv--UBtlcfqI4tE9JJmrwBjNnDriTothTowuafHey3eyuQlCkcAApZmT0K9P6PnLzXHaCWY391W2MOR0XaipgxuZ5LSu1W%2FiDQU4NHojUvlUEST9CYQOFRWufGeHPfSactJFJxVHxH2ucuEuTwptjkwreUYVXrHzeulp4mIj%2BTrEheXNywZeOnulWnG1yljSxCsK%2BU55AfKvcNpZJ5w6rpMeBd%2B5%2BIDci6ZsyQpaNHkalobk%2BcN7UzVCf35lfRbAdZuylTTiszIHtL%2Bms%2Fw5uLO1oM3axhr2cWKJ%2FO3zbJAIhlDYDNpJrzu78%3D%7Ctkp%3ABk9SR_jVlY-maA</t>
+  </si>
+  <si>
+    <t>USC Custom</t>
   </si>
 </sst>
 </file>
@@ -703,7 +706,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -782,6 +785,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2307,7 +2313,9 @@
       <c r="C41" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D41" s="26"/>
+      <c r="D41" s="30" t="s">
+        <v>189</v>
+      </c>
       <c r="E41" s="14">
         <v>1</v>
       </c>
@@ -2326,7 +2334,9 @@
       <c r="C42" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D42" s="26"/>
+      <c r="D42" s="30" t="s">
+        <v>189</v>
+      </c>
       <c r="E42" s="14">
         <v>1</v>
       </c>

--- a/system_development/v0.2.0/BOM-v0.2.0 .xlsx
+++ b/system_development/v0.2.0/BOM-v0.2.0 .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Fieldable-NV-Center\system_development\v0.2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shari\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E319474E-4949-4766-BA60-60104250321C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D122F8-5682-470A-9F7F-D91D6B704EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="196">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -606,6 +606,24 @@
   </si>
   <si>
     <t>USC Custom</t>
+  </si>
+  <si>
+    <t>DC Power Supply</t>
+  </si>
+  <si>
+    <t>B&amp;K Precision 1665</t>
+  </si>
+  <si>
+    <t>Bench Switching DC Power Supply, 1-19.99V, 0-9.99A</t>
+  </si>
+  <si>
+    <t>https://www.tequipment.net/BK/1665/DC-Power-Supplies/Lab-Power-Supplies/?gad_source=1&amp;gad_campaignid=23678563602&amp;gbraid=0AAAAAD_t4swRWL1d9G2a8mkSHmhxGMnXx&amp;gclid=CjwKCAjwrbfWBhAeEiwAc2e6Pj8HdVMyVd9n_YOFi7UwQfhRjzgiFBOOgm7V444cRC_QMr5OIOyaBRoCa3sQAvD_BwE</t>
+  </si>
+  <si>
+    <t>B&amp;K Precision 9201</t>
+  </si>
+  <si>
+    <t>Multi-Range Programmable DC Power Supply, 200W, 60V, 10A</t>
   </si>
 </sst>
 </file>
@@ -706,7 +724,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -784,8 +802,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1126,25 +1143,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:N48"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="62.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="62.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="87.5703125" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="83.42578125" customWidth="1"/>
-    <col min="12" max="12" width="62.42578125" customWidth="1"/>
-    <col min="13" max="13" width="55.85546875" customWidth="1"/>
+    <col min="9" max="9" width="87.5546875" customWidth="1"/>
+    <col min="10" max="10" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.44140625" customWidth="1"/>
+    <col min="12" max="12" width="62.44140625" customWidth="1"/>
+    <col min="13" max="13" width="55.88671875" customWidth="1"/>
     <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -1188,7 +1205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>17</v>
       </c>
@@ -1216,7 +1233,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>66</v>
       </c>
@@ -1244,7 +1261,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1274,7 +1291,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1304,7 +1321,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1331,7 +1348,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>69</v>
       </c>
@@ -1359,7 +1376,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>70</v>
       </c>
@@ -1388,7 +1405,7 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>71</v>
       </c>
@@ -1417,7 +1434,7 @@
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>43</v>
       </c>
@@ -1446,7 +1463,7 @@
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>43</v>
       </c>
@@ -1475,7 +1492,7 @@
       </c>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>72</v>
       </c>
@@ -1504,7 +1521,7 @@
       </c>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>53</v>
       </c>
@@ -1533,7 +1550,7 @@
       </c>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>73</v>
       </c>
@@ -1562,7 +1579,7 @@
       </c>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>74</v>
       </c>
@@ -1590,7 +1607,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>75</v>
       </c>
@@ -1619,7 +1636,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>76</v>
       </c>
@@ -1648,7 +1665,7 @@
       </c>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
         <v>81</v>
       </c>
@@ -1678,7 +1695,7 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>84</v>
       </c>
@@ -1708,7 +1725,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>88</v>
       </c>
@@ -1738,7 +1755,7 @@
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>92</v>
       </c>
@@ -1768,7 +1785,7 @@
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
         <v>96</v>
       </c>
@@ -1798,7 +1815,7 @@
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
         <v>101</v>
       </c>
@@ -1828,7 +1845,7 @@
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
         <v>106</v>
       </c>
@@ -1858,7 +1875,7 @@
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>108</v>
       </c>
@@ -1886,7 +1903,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>108</v>
       </c>
@@ -1914,7 +1931,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>112</v>
       </c>
@@ -1942,7 +1959,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>120</v>
       </c>
@@ -1970,7 +1987,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>127</v>
       </c>
@@ -1998,7 +2015,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>126</v>
       </c>
@@ -2026,7 +2043,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>131</v>
       </c>
@@ -2054,7 +2071,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>139</v>
       </c>
@@ -2082,7 +2099,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>138</v>
       </c>
@@ -2110,7 +2127,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>143</v>
       </c>
@@ -2138,7 +2155,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>147</v>
       </c>
@@ -2166,7 +2183,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>152</v>
       </c>
@@ -2194,7 +2211,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>155</v>
       </c>
@@ -2222,7 +2239,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>159</v>
       </c>
@@ -2249,7 +2266,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>170</v>
       </c>
@@ -2276,7 +2293,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>166</v>
       </c>
@@ -2303,7 +2320,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
         <v>174</v>
       </c>
@@ -2313,7 +2330,7 @@
       <c r="C41" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="29" t="s">
         <v>189</v>
       </c>
       <c r="E41" s="14">
@@ -2324,7 +2341,7 @@
       <c r="H41" s="4"/>
       <c r="I41" s="27"/>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>173</v>
       </c>
@@ -2334,7 +2351,7 @@
       <c r="C42" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="29" t="s">
         <v>189</v>
       </c>
       <c r="E42" s="14">
@@ -2345,7 +2362,7 @@
       <c r="H42" s="4"/>
       <c r="I42" s="27"/>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>175</v>
       </c>
@@ -2372,7 +2389,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>179</v>
       </c>
@@ -2399,7 +2416,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>179</v>
       </c>
@@ -2430,27 +2447,66 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="17"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="23"/>
+    <row r="46" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" t="s">
+        <v>192</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="14">
+        <v>1</v>
+      </c>
+      <c r="F46" s="15">
+        <v>389</v>
+      </c>
+      <c r="G46" s="23">
+        <v>389</v>
+      </c>
       <c r="H46" s="4"/>
-      <c r="I46" s="27"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F47" s="7" t="s">
+      <c r="I46" s="27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" t="s">
+        <v>194</v>
+      </c>
+      <c r="E47" s="14">
+        <v>1</v>
+      </c>
+      <c r="F47" s="15">
+        <v>805</v>
+      </c>
+      <c r="G47" s="15">
+        <v>805</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="27"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F48" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="5">
-        <f>SUM(G2:G45)</f>
-        <v>36844.39</v>
-      </c>
-      <c r="I47" s="29"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I48" s="29"/>
+      <c r="G48" s="5">
+        <f>SUM(G2:G47)</f>
+        <v>38038.39</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
